--- a/MIS-Task-Import-Template.xlsx
+++ b/MIS-Task-Import-Template.xlsx
@@ -679,7 +679,7 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>Ayesha Khan</t>
+          <t>Full name</t>
         </is>
       </c>
     </row>

--- a/MIS-Task-Import-Template.xlsx
+++ b/MIS-Task-Import-Template.xlsx
@@ -11,6 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tasks" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Members" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leaders" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Modules" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Tasks'!$1:$1</definedName>
@@ -552,7 +553,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -885,6 +886,18 @@
       <c r="A24" s="12" t="inlineStr">
         <is>
           <t>Computed columns such as Office Hours Spent and State are produced on export and ignored on import. This template contains no data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>Module (optional)</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Column L on the Tasks sheet: the module the task is against (list comes from the Modules sheet; you can also type a new module name).</t>
         </is>
       </c>
     </row>
@@ -911,7 +924,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K301"/>
+  <dimension ref="A1:L301"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -925,6 +938,7 @@
     <col width="11" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
     <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -981,6 +995,11 @@
       <c r="K1" s="13" t="inlineStr">
         <is>
           <t>Est Hours</t>
+        </is>
+      </c>
+      <c r="L1" s="13" t="inlineStr">
+        <is>
+          <t>Module</t>
         </is>
       </c>
     </row>
@@ -996,6 +1015,7 @@
       <c r="I2" s="15" t="n"/>
       <c r="J2" s="16" t="n"/>
       <c r="K2" s="15" t="n"/>
+      <c r="L2" s="15" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="17" t="n"/>
@@ -1009,6 +1029,7 @@
       <c r="I3" s="17" t="n"/>
       <c r="J3" s="18" t="n"/>
       <c r="K3" s="17" t="n"/>
+      <c r="L3" s="17" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="15" t="n"/>
@@ -1022,6 +1043,7 @@
       <c r="I4" s="15" t="n"/>
       <c r="J4" s="16" t="n"/>
       <c r="K4" s="15" t="n"/>
+      <c r="L4" s="15" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="17" t="n"/>
@@ -1035,6 +1057,7 @@
       <c r="I5" s="17" t="n"/>
       <c r="J5" s="18" t="n"/>
       <c r="K5" s="17" t="n"/>
+      <c r="L5" s="17" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="15" t="n"/>
@@ -1048,6 +1071,7 @@
       <c r="I6" s="15" t="n"/>
       <c r="J6" s="16" t="n"/>
       <c r="K6" s="15" t="n"/>
+      <c r="L6" s="15" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="17" t="n"/>
@@ -1061,6 +1085,7 @@
       <c r="I7" s="17" t="n"/>
       <c r="J7" s="18" t="n"/>
       <c r="K7" s="17" t="n"/>
+      <c r="L7" s="17" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="15" t="n"/>
@@ -1074,6 +1099,7 @@
       <c r="I8" s="15" t="n"/>
       <c r="J8" s="16" t="n"/>
       <c r="K8" s="15" t="n"/>
+      <c r="L8" s="15" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="17" t="n"/>
@@ -1087,6 +1113,7 @@
       <c r="I9" s="17" t="n"/>
       <c r="J9" s="18" t="n"/>
       <c r="K9" s="17" t="n"/>
+      <c r="L9" s="17" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="15" t="n"/>
@@ -1100,6 +1127,7 @@
       <c r="I10" s="15" t="n"/>
       <c r="J10" s="16" t="n"/>
       <c r="K10" s="15" t="n"/>
+      <c r="L10" s="15" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="17" t="n"/>
@@ -1113,6 +1141,7 @@
       <c r="I11" s="17" t="n"/>
       <c r="J11" s="18" t="n"/>
       <c r="K11" s="17" t="n"/>
+      <c r="L11" s="17" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="15" t="n"/>
@@ -1126,6 +1155,7 @@
       <c r="I12" s="15" t="n"/>
       <c r="J12" s="16" t="n"/>
       <c r="K12" s="15" t="n"/>
+      <c r="L12" s="15" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="17" t="n"/>
@@ -1139,6 +1169,7 @@
       <c r="I13" s="17" t="n"/>
       <c r="J13" s="18" t="n"/>
       <c r="K13" s="17" t="n"/>
+      <c r="L13" s="17" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="15" t="n"/>
@@ -1152,6 +1183,7 @@
       <c r="I14" s="15" t="n"/>
       <c r="J14" s="16" t="n"/>
       <c r="K14" s="15" t="n"/>
+      <c r="L14" s="15" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="17" t="n"/>
@@ -1165,6 +1197,7 @@
       <c r="I15" s="17" t="n"/>
       <c r="J15" s="18" t="n"/>
       <c r="K15" s="17" t="n"/>
+      <c r="L15" s="17" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="15" t="n"/>
@@ -1178,6 +1211,7 @@
       <c r="I16" s="15" t="n"/>
       <c r="J16" s="16" t="n"/>
       <c r="K16" s="15" t="n"/>
+      <c r="L16" s="15" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="17" t="n"/>
@@ -1191,6 +1225,7 @@
       <c r="I17" s="17" t="n"/>
       <c r="J17" s="18" t="n"/>
       <c r="K17" s="17" t="n"/>
+      <c r="L17" s="17" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="15" t="n"/>
@@ -1204,6 +1239,7 @@
       <c r="I18" s="15" t="n"/>
       <c r="J18" s="16" t="n"/>
       <c r="K18" s="15" t="n"/>
+      <c r="L18" s="15" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="17" t="n"/>
@@ -1217,6 +1253,7 @@
       <c r="I19" s="17" t="n"/>
       <c r="J19" s="18" t="n"/>
       <c r="K19" s="17" t="n"/>
+      <c r="L19" s="17" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="15" t="n"/>
@@ -1230,6 +1267,7 @@
       <c r="I20" s="15" t="n"/>
       <c r="J20" s="16" t="n"/>
       <c r="K20" s="15" t="n"/>
+      <c r="L20" s="15" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="17" t="n"/>
@@ -1243,6 +1281,7 @@
       <c r="I21" s="17" t="n"/>
       <c r="J21" s="18" t="n"/>
       <c r="K21" s="17" t="n"/>
+      <c r="L21" s="17" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="15" t="n"/>
@@ -1256,6 +1295,7 @@
       <c r="I22" s="15" t="n"/>
       <c r="J22" s="16" t="n"/>
       <c r="K22" s="15" t="n"/>
+      <c r="L22" s="15" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="17" t="n"/>
@@ -1269,6 +1309,7 @@
       <c r="I23" s="17" t="n"/>
       <c r="J23" s="18" t="n"/>
       <c r="K23" s="17" t="n"/>
+      <c r="L23" s="17" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="15" t="n"/>
@@ -1282,6 +1323,7 @@
       <c r="I24" s="15" t="n"/>
       <c r="J24" s="16" t="n"/>
       <c r="K24" s="15" t="n"/>
+      <c r="L24" s="15" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="17" t="n"/>
@@ -1295,6 +1337,7 @@
       <c r="I25" s="17" t="n"/>
       <c r="J25" s="18" t="n"/>
       <c r="K25" s="17" t="n"/>
+      <c r="L25" s="17" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="15" t="n"/>
@@ -1308,6 +1351,7 @@
       <c r="I26" s="15" t="n"/>
       <c r="J26" s="16" t="n"/>
       <c r="K26" s="15" t="n"/>
+      <c r="L26" s="15" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="17" t="n"/>
@@ -1321,6 +1365,7 @@
       <c r="I27" s="17" t="n"/>
       <c r="J27" s="18" t="n"/>
       <c r="K27" s="17" t="n"/>
+      <c r="L27" s="17" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="15" t="n"/>
@@ -1334,6 +1379,7 @@
       <c r="I28" s="15" t="n"/>
       <c r="J28" s="16" t="n"/>
       <c r="K28" s="15" t="n"/>
+      <c r="L28" s="15" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="17" t="n"/>
@@ -1347,6 +1393,7 @@
       <c r="I29" s="17" t="n"/>
       <c r="J29" s="18" t="n"/>
       <c r="K29" s="17" t="n"/>
+      <c r="L29" s="17" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="15" t="n"/>
@@ -1360,6 +1407,7 @@
       <c r="I30" s="15" t="n"/>
       <c r="J30" s="16" t="n"/>
       <c r="K30" s="15" t="n"/>
+      <c r="L30" s="15" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="17" t="n"/>
@@ -1373,6 +1421,7 @@
       <c r="I31" s="17" t="n"/>
       <c r="J31" s="18" t="n"/>
       <c r="K31" s="17" t="n"/>
+      <c r="L31" s="17" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="15" t="n"/>
@@ -1386,6 +1435,7 @@
       <c r="I32" s="15" t="n"/>
       <c r="J32" s="16" t="n"/>
       <c r="K32" s="15" t="n"/>
+      <c r="L32" s="15" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="17" t="n"/>
@@ -1399,6 +1449,7 @@
       <c r="I33" s="17" t="n"/>
       <c r="J33" s="18" t="n"/>
       <c r="K33" s="17" t="n"/>
+      <c r="L33" s="17" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="15" t="n"/>
@@ -1412,6 +1463,7 @@
       <c r="I34" s="15" t="n"/>
       <c r="J34" s="16" t="n"/>
       <c r="K34" s="15" t="n"/>
+      <c r="L34" s="15" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="17" t="n"/>
@@ -1425,6 +1477,7 @@
       <c r="I35" s="17" t="n"/>
       <c r="J35" s="18" t="n"/>
       <c r="K35" s="17" t="n"/>
+      <c r="L35" s="17" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="15" t="n"/>
@@ -1438,6 +1491,7 @@
       <c r="I36" s="15" t="n"/>
       <c r="J36" s="16" t="n"/>
       <c r="K36" s="15" t="n"/>
+      <c r="L36" s="15" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="17" t="n"/>
@@ -1451,6 +1505,7 @@
       <c r="I37" s="17" t="n"/>
       <c r="J37" s="18" t="n"/>
       <c r="K37" s="17" t="n"/>
+      <c r="L37" s="17" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="15" t="n"/>
@@ -1464,6 +1519,7 @@
       <c r="I38" s="15" t="n"/>
       <c r="J38" s="16" t="n"/>
       <c r="K38" s="15" t="n"/>
+      <c r="L38" s="15" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="17" t="n"/>
@@ -1477,6 +1533,7 @@
       <c r="I39" s="17" t="n"/>
       <c r="J39" s="18" t="n"/>
       <c r="K39" s="17" t="n"/>
+      <c r="L39" s="17" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="15" t="n"/>
@@ -1490,6 +1547,7 @@
       <c r="I40" s="15" t="n"/>
       <c r="J40" s="16" t="n"/>
       <c r="K40" s="15" t="n"/>
+      <c r="L40" s="15" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="17" t="n"/>
@@ -1503,6 +1561,7 @@
       <c r="I41" s="17" t="n"/>
       <c r="J41" s="18" t="n"/>
       <c r="K41" s="17" t="n"/>
+      <c r="L41" s="17" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="15" t="n"/>
@@ -1516,6 +1575,7 @@
       <c r="I42" s="15" t="n"/>
       <c r="J42" s="16" t="n"/>
       <c r="K42" s="15" t="n"/>
+      <c r="L42" s="15" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="17" t="n"/>
@@ -1529,6 +1589,7 @@
       <c r="I43" s="17" t="n"/>
       <c r="J43" s="18" t="n"/>
       <c r="K43" s="17" t="n"/>
+      <c r="L43" s="17" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="15" t="n"/>
@@ -1542,6 +1603,7 @@
       <c r="I44" s="15" t="n"/>
       <c r="J44" s="16" t="n"/>
       <c r="K44" s="15" t="n"/>
+      <c r="L44" s="15" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="17" t="n"/>
@@ -1555,6 +1617,7 @@
       <c r="I45" s="17" t="n"/>
       <c r="J45" s="18" t="n"/>
       <c r="K45" s="17" t="n"/>
+      <c r="L45" s="17" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="15" t="n"/>
@@ -1568,6 +1631,7 @@
       <c r="I46" s="15" t="n"/>
       <c r="J46" s="16" t="n"/>
       <c r="K46" s="15" t="n"/>
+      <c r="L46" s="15" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="17" t="n"/>
@@ -1581,6 +1645,7 @@
       <c r="I47" s="17" t="n"/>
       <c r="J47" s="18" t="n"/>
       <c r="K47" s="17" t="n"/>
+      <c r="L47" s="17" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="15" t="n"/>
@@ -1594,6 +1659,7 @@
       <c r="I48" s="15" t="n"/>
       <c r="J48" s="16" t="n"/>
       <c r="K48" s="15" t="n"/>
+      <c r="L48" s="15" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="17" t="n"/>
@@ -1607,6 +1673,7 @@
       <c r="I49" s="17" t="n"/>
       <c r="J49" s="18" t="n"/>
       <c r="K49" s="17" t="n"/>
+      <c r="L49" s="17" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="15" t="n"/>
@@ -1620,6 +1687,7 @@
       <c r="I50" s="15" t="n"/>
       <c r="J50" s="16" t="n"/>
       <c r="K50" s="15" t="n"/>
+      <c r="L50" s="15" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="17" t="n"/>
@@ -1633,6 +1701,7 @@
       <c r="I51" s="17" t="n"/>
       <c r="J51" s="18" t="n"/>
       <c r="K51" s="17" t="n"/>
+      <c r="L51" s="17" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="15" t="n"/>
@@ -1646,6 +1715,7 @@
       <c r="I52" s="15" t="n"/>
       <c r="J52" s="16" t="n"/>
       <c r="K52" s="15" t="n"/>
+      <c r="L52" s="15" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="17" t="n"/>
@@ -1659,6 +1729,7 @@
       <c r="I53" s="17" t="n"/>
       <c r="J53" s="18" t="n"/>
       <c r="K53" s="17" t="n"/>
+      <c r="L53" s="17" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="15" t="n"/>
@@ -1672,6 +1743,7 @@
       <c r="I54" s="15" t="n"/>
       <c r="J54" s="16" t="n"/>
       <c r="K54" s="15" t="n"/>
+      <c r="L54" s="15" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="17" t="n"/>
@@ -1685,6 +1757,7 @@
       <c r="I55" s="17" t="n"/>
       <c r="J55" s="18" t="n"/>
       <c r="K55" s="17" t="n"/>
+      <c r="L55" s="17" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="15" t="n"/>
@@ -1698,6 +1771,7 @@
       <c r="I56" s="15" t="n"/>
       <c r="J56" s="16" t="n"/>
       <c r="K56" s="15" t="n"/>
+      <c r="L56" s="15" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="17" t="n"/>
@@ -1711,6 +1785,7 @@
       <c r="I57" s="17" t="n"/>
       <c r="J57" s="18" t="n"/>
       <c r="K57" s="17" t="n"/>
+      <c r="L57" s="17" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="15" t="n"/>
@@ -1724,6 +1799,7 @@
       <c r="I58" s="15" t="n"/>
       <c r="J58" s="16" t="n"/>
       <c r="K58" s="15" t="n"/>
+      <c r="L58" s="15" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="17" t="n"/>
@@ -1737,6 +1813,7 @@
       <c r="I59" s="17" t="n"/>
       <c r="J59" s="18" t="n"/>
       <c r="K59" s="17" t="n"/>
+      <c r="L59" s="17" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="15" t="n"/>
@@ -1750,6 +1827,7 @@
       <c r="I60" s="15" t="n"/>
       <c r="J60" s="16" t="n"/>
       <c r="K60" s="15" t="n"/>
+      <c r="L60" s="15" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="17" t="n"/>
@@ -1763,6 +1841,7 @@
       <c r="I61" s="17" t="n"/>
       <c r="J61" s="18" t="n"/>
       <c r="K61" s="17" t="n"/>
+      <c r="L61" s="17" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="15" t="n"/>
@@ -1776,6 +1855,7 @@
       <c r="I62" s="15" t="n"/>
       <c r="J62" s="16" t="n"/>
       <c r="K62" s="15" t="n"/>
+      <c r="L62" s="15" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="17" t="n"/>
@@ -1789,6 +1869,7 @@
       <c r="I63" s="17" t="n"/>
       <c r="J63" s="18" t="n"/>
       <c r="K63" s="17" t="n"/>
+      <c r="L63" s="17" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="15" t="n"/>
@@ -1802,6 +1883,7 @@
       <c r="I64" s="15" t="n"/>
       <c r="J64" s="16" t="n"/>
       <c r="K64" s="15" t="n"/>
+      <c r="L64" s="15" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="17" t="n"/>
@@ -1815,6 +1897,7 @@
       <c r="I65" s="17" t="n"/>
       <c r="J65" s="18" t="n"/>
       <c r="K65" s="17" t="n"/>
+      <c r="L65" s="17" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="15" t="n"/>
@@ -1828,6 +1911,7 @@
       <c r="I66" s="15" t="n"/>
       <c r="J66" s="16" t="n"/>
       <c r="K66" s="15" t="n"/>
+      <c r="L66" s="15" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="17" t="n"/>
@@ -1841,6 +1925,7 @@
       <c r="I67" s="17" t="n"/>
       <c r="J67" s="18" t="n"/>
       <c r="K67" s="17" t="n"/>
+      <c r="L67" s="17" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="15" t="n"/>
@@ -1854,6 +1939,7 @@
       <c r="I68" s="15" t="n"/>
       <c r="J68" s="16" t="n"/>
       <c r="K68" s="15" t="n"/>
+      <c r="L68" s="15" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="17" t="n"/>
@@ -1867,6 +1953,7 @@
       <c r="I69" s="17" t="n"/>
       <c r="J69" s="18" t="n"/>
       <c r="K69" s="17" t="n"/>
+      <c r="L69" s="17" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="15" t="n"/>
@@ -1880,6 +1967,7 @@
       <c r="I70" s="15" t="n"/>
       <c r="J70" s="16" t="n"/>
       <c r="K70" s="15" t="n"/>
+      <c r="L70" s="15" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="17" t="n"/>
@@ -1893,6 +1981,7 @@
       <c r="I71" s="17" t="n"/>
       <c r="J71" s="18" t="n"/>
       <c r="K71" s="17" t="n"/>
+      <c r="L71" s="17" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="15" t="n"/>
@@ -1906,6 +1995,7 @@
       <c r="I72" s="15" t="n"/>
       <c r="J72" s="16" t="n"/>
       <c r="K72" s="15" t="n"/>
+      <c r="L72" s="15" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="17" t="n"/>
@@ -1919,6 +2009,7 @@
       <c r="I73" s="17" t="n"/>
       <c r="J73" s="18" t="n"/>
       <c r="K73" s="17" t="n"/>
+      <c r="L73" s="17" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="15" t="n"/>
@@ -1932,6 +2023,7 @@
       <c r="I74" s="15" t="n"/>
       <c r="J74" s="16" t="n"/>
       <c r="K74" s="15" t="n"/>
+      <c r="L74" s="15" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="17" t="n"/>
@@ -1945,6 +2037,7 @@
       <c r="I75" s="17" t="n"/>
       <c r="J75" s="18" t="n"/>
       <c r="K75" s="17" t="n"/>
+      <c r="L75" s="17" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="15" t="n"/>
@@ -1958,6 +2051,7 @@
       <c r="I76" s="15" t="n"/>
       <c r="J76" s="16" t="n"/>
       <c r="K76" s="15" t="n"/>
+      <c r="L76" s="15" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="17" t="n"/>
@@ -1971,6 +2065,7 @@
       <c r="I77" s="17" t="n"/>
       <c r="J77" s="18" t="n"/>
       <c r="K77" s="17" t="n"/>
+      <c r="L77" s="17" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="15" t="n"/>
@@ -1984,6 +2079,7 @@
       <c r="I78" s="15" t="n"/>
       <c r="J78" s="16" t="n"/>
       <c r="K78" s="15" t="n"/>
+      <c r="L78" s="15" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="17" t="n"/>
@@ -1997,6 +2093,7 @@
       <c r="I79" s="17" t="n"/>
       <c r="J79" s="18" t="n"/>
       <c r="K79" s="17" t="n"/>
+      <c r="L79" s="17" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="15" t="n"/>
@@ -2010,6 +2107,7 @@
       <c r="I80" s="15" t="n"/>
       <c r="J80" s="16" t="n"/>
       <c r="K80" s="15" t="n"/>
+      <c r="L80" s="15" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="17" t="n"/>
@@ -2023,6 +2121,7 @@
       <c r="I81" s="17" t="n"/>
       <c r="J81" s="18" t="n"/>
       <c r="K81" s="17" t="n"/>
+      <c r="L81" s="17" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="15" t="n"/>
@@ -2036,6 +2135,7 @@
       <c r="I82" s="15" t="n"/>
       <c r="J82" s="16" t="n"/>
       <c r="K82" s="15" t="n"/>
+      <c r="L82" s="15" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="17" t="n"/>
@@ -2049,6 +2149,7 @@
       <c r="I83" s="17" t="n"/>
       <c r="J83" s="18" t="n"/>
       <c r="K83" s="17" t="n"/>
+      <c r="L83" s="17" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="15" t="n"/>
@@ -2062,6 +2163,7 @@
       <c r="I84" s="15" t="n"/>
       <c r="J84" s="16" t="n"/>
       <c r="K84" s="15" t="n"/>
+      <c r="L84" s="15" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="17" t="n"/>
@@ -2075,6 +2177,7 @@
       <c r="I85" s="17" t="n"/>
       <c r="J85" s="18" t="n"/>
       <c r="K85" s="17" t="n"/>
+      <c r="L85" s="17" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="15" t="n"/>
@@ -2088,6 +2191,7 @@
       <c r="I86" s="15" t="n"/>
       <c r="J86" s="16" t="n"/>
       <c r="K86" s="15" t="n"/>
+      <c r="L86" s="15" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="17" t="n"/>
@@ -2101,6 +2205,7 @@
       <c r="I87" s="17" t="n"/>
       <c r="J87" s="18" t="n"/>
       <c r="K87" s="17" t="n"/>
+      <c r="L87" s="17" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="15" t="n"/>
@@ -2114,6 +2219,7 @@
       <c r="I88" s="15" t="n"/>
       <c r="J88" s="16" t="n"/>
       <c r="K88" s="15" t="n"/>
+      <c r="L88" s="15" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="17" t="n"/>
@@ -2127,6 +2233,7 @@
       <c r="I89" s="17" t="n"/>
       <c r="J89" s="18" t="n"/>
       <c r="K89" s="17" t="n"/>
+      <c r="L89" s="17" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="15" t="n"/>
@@ -2140,6 +2247,7 @@
       <c r="I90" s="15" t="n"/>
       <c r="J90" s="16" t="n"/>
       <c r="K90" s="15" t="n"/>
+      <c r="L90" s="15" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="17" t="n"/>
@@ -2153,6 +2261,7 @@
       <c r="I91" s="17" t="n"/>
       <c r="J91" s="18" t="n"/>
       <c r="K91" s="17" t="n"/>
+      <c r="L91" s="17" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="15" t="n"/>
@@ -2166,6 +2275,7 @@
       <c r="I92" s="15" t="n"/>
       <c r="J92" s="16" t="n"/>
       <c r="K92" s="15" t="n"/>
+      <c r="L92" s="15" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="17" t="n"/>
@@ -2179,6 +2289,7 @@
       <c r="I93" s="17" t="n"/>
       <c r="J93" s="18" t="n"/>
       <c r="K93" s="17" t="n"/>
+      <c r="L93" s="17" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="15" t="n"/>
@@ -2192,6 +2303,7 @@
       <c r="I94" s="15" t="n"/>
       <c r="J94" s="16" t="n"/>
       <c r="K94" s="15" t="n"/>
+      <c r="L94" s="15" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="17" t="n"/>
@@ -2205,6 +2317,7 @@
       <c r="I95" s="17" t="n"/>
       <c r="J95" s="18" t="n"/>
       <c r="K95" s="17" t="n"/>
+      <c r="L95" s="17" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="15" t="n"/>
@@ -2218,6 +2331,7 @@
       <c r="I96" s="15" t="n"/>
       <c r="J96" s="16" t="n"/>
       <c r="K96" s="15" t="n"/>
+      <c r="L96" s="15" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="17" t="n"/>
@@ -2231,6 +2345,7 @@
       <c r="I97" s="17" t="n"/>
       <c r="J97" s="18" t="n"/>
       <c r="K97" s="17" t="n"/>
+      <c r="L97" s="17" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="15" t="n"/>
@@ -2244,6 +2359,7 @@
       <c r="I98" s="15" t="n"/>
       <c r="J98" s="16" t="n"/>
       <c r="K98" s="15" t="n"/>
+      <c r="L98" s="15" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="17" t="n"/>
@@ -2257,6 +2373,7 @@
       <c r="I99" s="17" t="n"/>
       <c r="J99" s="18" t="n"/>
       <c r="K99" s="17" t="n"/>
+      <c r="L99" s="17" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="15" t="n"/>
@@ -2270,6 +2387,7 @@
       <c r="I100" s="15" t="n"/>
       <c r="J100" s="16" t="n"/>
       <c r="K100" s="15" t="n"/>
+      <c r="L100" s="15" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="17" t="n"/>
@@ -2283,6 +2401,7 @@
       <c r="I101" s="17" t="n"/>
       <c r="J101" s="18" t="n"/>
       <c r="K101" s="17" t="n"/>
+      <c r="L101" s="17" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="15" t="n"/>
@@ -2296,6 +2415,7 @@
       <c r="I102" s="15" t="n"/>
       <c r="J102" s="16" t="n"/>
       <c r="K102" s="15" t="n"/>
+      <c r="L102" s="15" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="17" t="n"/>
@@ -2309,6 +2429,7 @@
       <c r="I103" s="17" t="n"/>
       <c r="J103" s="18" t="n"/>
       <c r="K103" s="17" t="n"/>
+      <c r="L103" s="17" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="15" t="n"/>
@@ -2322,6 +2443,7 @@
       <c r="I104" s="15" t="n"/>
       <c r="J104" s="16" t="n"/>
       <c r="K104" s="15" t="n"/>
+      <c r="L104" s="15" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="17" t="n"/>
@@ -2335,6 +2457,7 @@
       <c r="I105" s="17" t="n"/>
       <c r="J105" s="18" t="n"/>
       <c r="K105" s="17" t="n"/>
+      <c r="L105" s="17" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="15" t="n"/>
@@ -2348,6 +2471,7 @@
       <c r="I106" s="15" t="n"/>
       <c r="J106" s="16" t="n"/>
       <c r="K106" s="15" t="n"/>
+      <c r="L106" s="15" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="17" t="n"/>
@@ -2361,6 +2485,7 @@
       <c r="I107" s="17" t="n"/>
       <c r="J107" s="18" t="n"/>
       <c r="K107" s="17" t="n"/>
+      <c r="L107" s="17" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="15" t="n"/>
@@ -2374,6 +2499,7 @@
       <c r="I108" s="15" t="n"/>
       <c r="J108" s="16" t="n"/>
       <c r="K108" s="15" t="n"/>
+      <c r="L108" s="15" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="17" t="n"/>
@@ -2387,6 +2513,7 @@
       <c r="I109" s="17" t="n"/>
       <c r="J109" s="18" t="n"/>
       <c r="K109" s="17" t="n"/>
+      <c r="L109" s="17" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="15" t="n"/>
@@ -2400,6 +2527,7 @@
       <c r="I110" s="15" t="n"/>
       <c r="J110" s="16" t="n"/>
       <c r="K110" s="15" t="n"/>
+      <c r="L110" s="15" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="17" t="n"/>
@@ -2413,6 +2541,7 @@
       <c r="I111" s="17" t="n"/>
       <c r="J111" s="18" t="n"/>
       <c r="K111" s="17" t="n"/>
+      <c r="L111" s="17" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="15" t="n"/>
@@ -2426,6 +2555,7 @@
       <c r="I112" s="15" t="n"/>
       <c r="J112" s="16" t="n"/>
       <c r="K112" s="15" t="n"/>
+      <c r="L112" s="15" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="17" t="n"/>
@@ -2439,6 +2569,7 @@
       <c r="I113" s="17" t="n"/>
       <c r="J113" s="18" t="n"/>
       <c r="K113" s="17" t="n"/>
+      <c r="L113" s="17" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="15" t="n"/>
@@ -2452,6 +2583,7 @@
       <c r="I114" s="15" t="n"/>
       <c r="J114" s="16" t="n"/>
       <c r="K114" s="15" t="n"/>
+      <c r="L114" s="15" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="17" t="n"/>
@@ -2465,6 +2597,7 @@
       <c r="I115" s="17" t="n"/>
       <c r="J115" s="18" t="n"/>
       <c r="K115" s="17" t="n"/>
+      <c r="L115" s="17" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="15" t="n"/>
@@ -2478,6 +2611,7 @@
       <c r="I116" s="15" t="n"/>
       <c r="J116" s="16" t="n"/>
       <c r="K116" s="15" t="n"/>
+      <c r="L116" s="15" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="17" t="n"/>
@@ -2491,6 +2625,7 @@
       <c r="I117" s="17" t="n"/>
       <c r="J117" s="18" t="n"/>
       <c r="K117" s="17" t="n"/>
+      <c r="L117" s="17" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="15" t="n"/>
@@ -2504,6 +2639,7 @@
       <c r="I118" s="15" t="n"/>
       <c r="J118" s="16" t="n"/>
       <c r="K118" s="15" t="n"/>
+      <c r="L118" s="15" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="17" t="n"/>
@@ -2517,6 +2653,7 @@
       <c r="I119" s="17" t="n"/>
       <c r="J119" s="18" t="n"/>
       <c r="K119" s="17" t="n"/>
+      <c r="L119" s="17" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="15" t="n"/>
@@ -2530,6 +2667,7 @@
       <c r="I120" s="15" t="n"/>
       <c r="J120" s="16" t="n"/>
       <c r="K120" s="15" t="n"/>
+      <c r="L120" s="15" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="17" t="n"/>
@@ -2543,6 +2681,7 @@
       <c r="I121" s="17" t="n"/>
       <c r="J121" s="18" t="n"/>
       <c r="K121" s="17" t="n"/>
+      <c r="L121" s="17" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="15" t="n"/>
@@ -2556,6 +2695,7 @@
       <c r="I122" s="15" t="n"/>
       <c r="J122" s="16" t="n"/>
       <c r="K122" s="15" t="n"/>
+      <c r="L122" s="15" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="17" t="n"/>
@@ -2569,6 +2709,7 @@
       <c r="I123" s="17" t="n"/>
       <c r="J123" s="18" t="n"/>
       <c r="K123" s="17" t="n"/>
+      <c r="L123" s="17" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="15" t="n"/>
@@ -2582,6 +2723,7 @@
       <c r="I124" s="15" t="n"/>
       <c r="J124" s="16" t="n"/>
       <c r="K124" s="15" t="n"/>
+      <c r="L124" s="15" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="17" t="n"/>
@@ -2595,6 +2737,7 @@
       <c r="I125" s="17" t="n"/>
       <c r="J125" s="18" t="n"/>
       <c r="K125" s="17" t="n"/>
+      <c r="L125" s="17" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="15" t="n"/>
@@ -2608,6 +2751,7 @@
       <c r="I126" s="15" t="n"/>
       <c r="J126" s="16" t="n"/>
       <c r="K126" s="15" t="n"/>
+      <c r="L126" s="15" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="17" t="n"/>
@@ -2621,6 +2765,7 @@
       <c r="I127" s="17" t="n"/>
       <c r="J127" s="18" t="n"/>
       <c r="K127" s="17" t="n"/>
+      <c r="L127" s="17" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="15" t="n"/>
@@ -2634,6 +2779,7 @@
       <c r="I128" s="15" t="n"/>
       <c r="J128" s="16" t="n"/>
       <c r="K128" s="15" t="n"/>
+      <c r="L128" s="15" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="17" t="n"/>
@@ -2647,6 +2793,7 @@
       <c r="I129" s="17" t="n"/>
       <c r="J129" s="18" t="n"/>
       <c r="K129" s="17" t="n"/>
+      <c r="L129" s="17" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="15" t="n"/>
@@ -2660,6 +2807,7 @@
       <c r="I130" s="15" t="n"/>
       <c r="J130" s="16" t="n"/>
       <c r="K130" s="15" t="n"/>
+      <c r="L130" s="15" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="17" t="n"/>
@@ -2673,6 +2821,7 @@
       <c r="I131" s="17" t="n"/>
       <c r="J131" s="18" t="n"/>
       <c r="K131" s="17" t="n"/>
+      <c r="L131" s="17" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="15" t="n"/>
@@ -2686,6 +2835,7 @@
       <c r="I132" s="15" t="n"/>
       <c r="J132" s="16" t="n"/>
       <c r="K132" s="15" t="n"/>
+      <c r="L132" s="15" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="17" t="n"/>
@@ -2699,6 +2849,7 @@
       <c r="I133" s="17" t="n"/>
       <c r="J133" s="18" t="n"/>
       <c r="K133" s="17" t="n"/>
+      <c r="L133" s="17" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="15" t="n"/>
@@ -2712,6 +2863,7 @@
       <c r="I134" s="15" t="n"/>
       <c r="J134" s="16" t="n"/>
       <c r="K134" s="15" t="n"/>
+      <c r="L134" s="15" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="17" t="n"/>
@@ -2725,6 +2877,7 @@
       <c r="I135" s="17" t="n"/>
       <c r="J135" s="18" t="n"/>
       <c r="K135" s="17" t="n"/>
+      <c r="L135" s="17" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="15" t="n"/>
@@ -2738,6 +2891,7 @@
       <c r="I136" s="15" t="n"/>
       <c r="J136" s="16" t="n"/>
       <c r="K136" s="15" t="n"/>
+      <c r="L136" s="15" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="17" t="n"/>
@@ -2751,6 +2905,7 @@
       <c r="I137" s="17" t="n"/>
       <c r="J137" s="18" t="n"/>
       <c r="K137" s="17" t="n"/>
+      <c r="L137" s="17" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="15" t="n"/>
@@ -2764,6 +2919,7 @@
       <c r="I138" s="15" t="n"/>
       <c r="J138" s="16" t="n"/>
       <c r="K138" s="15" t="n"/>
+      <c r="L138" s="15" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="17" t="n"/>
@@ -2777,6 +2933,7 @@
       <c r="I139" s="17" t="n"/>
       <c r="J139" s="18" t="n"/>
       <c r="K139" s="17" t="n"/>
+      <c r="L139" s="17" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="15" t="n"/>
@@ -2790,6 +2947,7 @@
       <c r="I140" s="15" t="n"/>
       <c r="J140" s="16" t="n"/>
       <c r="K140" s="15" t="n"/>
+      <c r="L140" s="15" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="17" t="n"/>
@@ -2803,6 +2961,7 @@
       <c r="I141" s="17" t="n"/>
       <c r="J141" s="18" t="n"/>
       <c r="K141" s="17" t="n"/>
+      <c r="L141" s="17" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="15" t="n"/>
@@ -2816,6 +2975,7 @@
       <c r="I142" s="15" t="n"/>
       <c r="J142" s="16" t="n"/>
       <c r="K142" s="15" t="n"/>
+      <c r="L142" s="15" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="17" t="n"/>
@@ -2829,6 +2989,7 @@
       <c r="I143" s="17" t="n"/>
       <c r="J143" s="18" t="n"/>
       <c r="K143" s="17" t="n"/>
+      <c r="L143" s="17" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="15" t="n"/>
@@ -2842,6 +3003,7 @@
       <c r="I144" s="15" t="n"/>
       <c r="J144" s="16" t="n"/>
       <c r="K144" s="15" t="n"/>
+      <c r="L144" s="15" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="17" t="n"/>
@@ -2855,6 +3017,7 @@
       <c r="I145" s="17" t="n"/>
       <c r="J145" s="18" t="n"/>
       <c r="K145" s="17" t="n"/>
+      <c r="L145" s="17" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="15" t="n"/>
@@ -2868,6 +3031,7 @@
       <c r="I146" s="15" t="n"/>
       <c r="J146" s="16" t="n"/>
       <c r="K146" s="15" t="n"/>
+      <c r="L146" s="15" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="17" t="n"/>
@@ -2881,6 +3045,7 @@
       <c r="I147" s="17" t="n"/>
       <c r="J147" s="18" t="n"/>
       <c r="K147" s="17" t="n"/>
+      <c r="L147" s="17" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="15" t="n"/>
@@ -2894,6 +3059,7 @@
       <c r="I148" s="15" t="n"/>
       <c r="J148" s="16" t="n"/>
       <c r="K148" s="15" t="n"/>
+      <c r="L148" s="15" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="17" t="n"/>
@@ -2907,6 +3073,7 @@
       <c r="I149" s="17" t="n"/>
       <c r="J149" s="18" t="n"/>
       <c r="K149" s="17" t="n"/>
+      <c r="L149" s="17" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="15" t="n"/>
@@ -2920,6 +3087,7 @@
       <c r="I150" s="15" t="n"/>
       <c r="J150" s="16" t="n"/>
       <c r="K150" s="15" t="n"/>
+      <c r="L150" s="15" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="17" t="n"/>
@@ -2933,6 +3101,7 @@
       <c r="I151" s="17" t="n"/>
       <c r="J151" s="18" t="n"/>
       <c r="K151" s="17" t="n"/>
+      <c r="L151" s="17" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="15" t="n"/>
@@ -2946,6 +3115,7 @@
       <c r="I152" s="15" t="n"/>
       <c r="J152" s="16" t="n"/>
       <c r="K152" s="15" t="n"/>
+      <c r="L152" s="15" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="17" t="n"/>
@@ -2959,6 +3129,7 @@
       <c r="I153" s="17" t="n"/>
       <c r="J153" s="18" t="n"/>
       <c r="K153" s="17" t="n"/>
+      <c r="L153" s="17" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="15" t="n"/>
@@ -2972,6 +3143,7 @@
       <c r="I154" s="15" t="n"/>
       <c r="J154" s="16" t="n"/>
       <c r="K154" s="15" t="n"/>
+      <c r="L154" s="15" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="17" t="n"/>
@@ -2985,6 +3157,7 @@
       <c r="I155" s="17" t="n"/>
       <c r="J155" s="18" t="n"/>
       <c r="K155" s="17" t="n"/>
+      <c r="L155" s="17" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="15" t="n"/>
@@ -2998,6 +3171,7 @@
       <c r="I156" s="15" t="n"/>
       <c r="J156" s="16" t="n"/>
       <c r="K156" s="15" t="n"/>
+      <c r="L156" s="15" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="17" t="n"/>
@@ -3011,6 +3185,7 @@
       <c r="I157" s="17" t="n"/>
       <c r="J157" s="18" t="n"/>
       <c r="K157" s="17" t="n"/>
+      <c r="L157" s="17" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="15" t="n"/>
@@ -3024,6 +3199,7 @@
       <c r="I158" s="15" t="n"/>
       <c r="J158" s="16" t="n"/>
       <c r="K158" s="15" t="n"/>
+      <c r="L158" s="15" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="17" t="n"/>
@@ -3037,6 +3213,7 @@
       <c r="I159" s="17" t="n"/>
       <c r="J159" s="18" t="n"/>
       <c r="K159" s="17" t="n"/>
+      <c r="L159" s="17" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="15" t="n"/>
@@ -3050,6 +3227,7 @@
       <c r="I160" s="15" t="n"/>
       <c r="J160" s="16" t="n"/>
       <c r="K160" s="15" t="n"/>
+      <c r="L160" s="15" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="17" t="n"/>
@@ -3063,6 +3241,7 @@
       <c r="I161" s="17" t="n"/>
       <c r="J161" s="18" t="n"/>
       <c r="K161" s="17" t="n"/>
+      <c r="L161" s="17" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="15" t="n"/>
@@ -3076,6 +3255,7 @@
       <c r="I162" s="15" t="n"/>
       <c r="J162" s="16" t="n"/>
       <c r="K162" s="15" t="n"/>
+      <c r="L162" s="15" t="n"/>
     </row>
     <row r="163">
       <c r="A163" s="17" t="n"/>
@@ -3089,6 +3269,7 @@
       <c r="I163" s="17" t="n"/>
       <c r="J163" s="18" t="n"/>
       <c r="K163" s="17" t="n"/>
+      <c r="L163" s="17" t="n"/>
     </row>
     <row r="164">
       <c r="A164" s="15" t="n"/>
@@ -3102,6 +3283,7 @@
       <c r="I164" s="15" t="n"/>
       <c r="J164" s="16" t="n"/>
       <c r="K164" s="15" t="n"/>
+      <c r="L164" s="15" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="17" t="n"/>
@@ -3115,6 +3297,7 @@
       <c r="I165" s="17" t="n"/>
       <c r="J165" s="18" t="n"/>
       <c r="K165" s="17" t="n"/>
+      <c r="L165" s="17" t="n"/>
     </row>
     <row r="166">
       <c r="A166" s="15" t="n"/>
@@ -3128,6 +3311,7 @@
       <c r="I166" s="15" t="n"/>
       <c r="J166" s="16" t="n"/>
       <c r="K166" s="15" t="n"/>
+      <c r="L166" s="15" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="17" t="n"/>
@@ -3141,6 +3325,7 @@
       <c r="I167" s="17" t="n"/>
       <c r="J167" s="18" t="n"/>
       <c r="K167" s="17" t="n"/>
+      <c r="L167" s="17" t="n"/>
     </row>
     <row r="168">
       <c r="A168" s="15" t="n"/>
@@ -3154,6 +3339,7 @@
       <c r="I168" s="15" t="n"/>
       <c r="J168" s="16" t="n"/>
       <c r="K168" s="15" t="n"/>
+      <c r="L168" s="15" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="17" t="n"/>
@@ -3167,6 +3353,7 @@
       <c r="I169" s="17" t="n"/>
       <c r="J169" s="18" t="n"/>
       <c r="K169" s="17" t="n"/>
+      <c r="L169" s="17" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="15" t="n"/>
@@ -3180,6 +3367,7 @@
       <c r="I170" s="15" t="n"/>
       <c r="J170" s="16" t="n"/>
       <c r="K170" s="15" t="n"/>
+      <c r="L170" s="15" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="17" t="n"/>
@@ -3193,6 +3381,7 @@
       <c r="I171" s="17" t="n"/>
       <c r="J171" s="18" t="n"/>
       <c r="K171" s="17" t="n"/>
+      <c r="L171" s="17" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="15" t="n"/>
@@ -3206,6 +3395,7 @@
       <c r="I172" s="15" t="n"/>
       <c r="J172" s="16" t="n"/>
       <c r="K172" s="15" t="n"/>
+      <c r="L172" s="15" t="n"/>
     </row>
     <row r="173">
       <c r="A173" s="17" t="n"/>
@@ -3219,6 +3409,7 @@
       <c r="I173" s="17" t="n"/>
       <c r="J173" s="18" t="n"/>
       <c r="K173" s="17" t="n"/>
+      <c r="L173" s="17" t="n"/>
     </row>
     <row r="174">
       <c r="A174" s="15" t="n"/>
@@ -3232,6 +3423,7 @@
       <c r="I174" s="15" t="n"/>
       <c r="J174" s="16" t="n"/>
       <c r="K174" s="15" t="n"/>
+      <c r="L174" s="15" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="17" t="n"/>
@@ -3245,6 +3437,7 @@
       <c r="I175" s="17" t="n"/>
       <c r="J175" s="18" t="n"/>
       <c r="K175" s="17" t="n"/>
+      <c r="L175" s="17" t="n"/>
     </row>
     <row r="176">
       <c r="A176" s="15" t="n"/>
@@ -3258,6 +3451,7 @@
       <c r="I176" s="15" t="n"/>
       <c r="J176" s="16" t="n"/>
       <c r="K176" s="15" t="n"/>
+      <c r="L176" s="15" t="n"/>
     </row>
     <row r="177">
       <c r="A177" s="17" t="n"/>
@@ -3271,6 +3465,7 @@
       <c r="I177" s="17" t="n"/>
       <c r="J177" s="18" t="n"/>
       <c r="K177" s="17" t="n"/>
+      <c r="L177" s="17" t="n"/>
     </row>
     <row r="178">
       <c r="A178" s="15" t="n"/>
@@ -3284,6 +3479,7 @@
       <c r="I178" s="15" t="n"/>
       <c r="J178" s="16" t="n"/>
       <c r="K178" s="15" t="n"/>
+      <c r="L178" s="15" t="n"/>
     </row>
     <row r="179">
       <c r="A179" s="17" t="n"/>
@@ -3297,6 +3493,7 @@
       <c r="I179" s="17" t="n"/>
       <c r="J179" s="18" t="n"/>
       <c r="K179" s="17" t="n"/>
+      <c r="L179" s="17" t="n"/>
     </row>
     <row r="180">
       <c r="A180" s="15" t="n"/>
@@ -3310,6 +3507,7 @@
       <c r="I180" s="15" t="n"/>
       <c r="J180" s="16" t="n"/>
       <c r="K180" s="15" t="n"/>
+      <c r="L180" s="15" t="n"/>
     </row>
     <row r="181">
       <c r="A181" s="17" t="n"/>
@@ -3323,6 +3521,7 @@
       <c r="I181" s="17" t="n"/>
       <c r="J181" s="18" t="n"/>
       <c r="K181" s="17" t="n"/>
+      <c r="L181" s="17" t="n"/>
     </row>
     <row r="182">
       <c r="A182" s="15" t="n"/>
@@ -3336,6 +3535,7 @@
       <c r="I182" s="15" t="n"/>
       <c r="J182" s="16" t="n"/>
       <c r="K182" s="15" t="n"/>
+      <c r="L182" s="15" t="n"/>
     </row>
     <row r="183">
       <c r="A183" s="17" t="n"/>
@@ -3349,6 +3549,7 @@
       <c r="I183" s="17" t="n"/>
       <c r="J183" s="18" t="n"/>
       <c r="K183" s="17" t="n"/>
+      <c r="L183" s="17" t="n"/>
     </row>
     <row r="184">
       <c r="A184" s="15" t="n"/>
@@ -3362,6 +3563,7 @@
       <c r="I184" s="15" t="n"/>
       <c r="J184" s="16" t="n"/>
       <c r="K184" s="15" t="n"/>
+      <c r="L184" s="15" t="n"/>
     </row>
     <row r="185">
       <c r="A185" s="17" t="n"/>
@@ -3375,6 +3577,7 @@
       <c r="I185" s="17" t="n"/>
       <c r="J185" s="18" t="n"/>
       <c r="K185" s="17" t="n"/>
+      <c r="L185" s="17" t="n"/>
     </row>
     <row r="186">
       <c r="A186" s="15" t="n"/>
@@ -3388,6 +3591,7 @@
       <c r="I186" s="15" t="n"/>
       <c r="J186" s="16" t="n"/>
       <c r="K186" s="15" t="n"/>
+      <c r="L186" s="15" t="n"/>
     </row>
     <row r="187">
       <c r="A187" s="17" t="n"/>
@@ -3401,6 +3605,7 @@
       <c r="I187" s="17" t="n"/>
       <c r="J187" s="18" t="n"/>
       <c r="K187" s="17" t="n"/>
+      <c r="L187" s="17" t="n"/>
     </row>
     <row r="188">
       <c r="A188" s="15" t="n"/>
@@ -3414,6 +3619,7 @@
       <c r="I188" s="15" t="n"/>
       <c r="J188" s="16" t="n"/>
       <c r="K188" s="15" t="n"/>
+      <c r="L188" s="15" t="n"/>
     </row>
     <row r="189">
       <c r="A189" s="17" t="n"/>
@@ -3427,6 +3633,7 @@
       <c r="I189" s="17" t="n"/>
       <c r="J189" s="18" t="n"/>
       <c r="K189" s="17" t="n"/>
+      <c r="L189" s="17" t="n"/>
     </row>
     <row r="190">
       <c r="A190" s="15" t="n"/>
@@ -3440,6 +3647,7 @@
       <c r="I190" s="15" t="n"/>
       <c r="J190" s="16" t="n"/>
       <c r="K190" s="15" t="n"/>
+      <c r="L190" s="15" t="n"/>
     </row>
     <row r="191">
       <c r="A191" s="17" t="n"/>
@@ -3453,6 +3661,7 @@
       <c r="I191" s="17" t="n"/>
       <c r="J191" s="18" t="n"/>
       <c r="K191" s="17" t="n"/>
+      <c r="L191" s="17" t="n"/>
     </row>
     <row r="192">
       <c r="A192" s="15" t="n"/>
@@ -3466,6 +3675,7 @@
       <c r="I192" s="15" t="n"/>
       <c r="J192" s="16" t="n"/>
       <c r="K192" s="15" t="n"/>
+      <c r="L192" s="15" t="n"/>
     </row>
     <row r="193">
       <c r="A193" s="17" t="n"/>
@@ -3479,6 +3689,7 @@
       <c r="I193" s="17" t="n"/>
       <c r="J193" s="18" t="n"/>
       <c r="K193" s="17" t="n"/>
+      <c r="L193" s="17" t="n"/>
     </row>
     <row r="194">
       <c r="A194" s="15" t="n"/>
@@ -3492,6 +3703,7 @@
       <c r="I194" s="15" t="n"/>
       <c r="J194" s="16" t="n"/>
       <c r="K194" s="15" t="n"/>
+      <c r="L194" s="15" t="n"/>
     </row>
     <row r="195">
       <c r="A195" s="17" t="n"/>
@@ -3505,6 +3717,7 @@
       <c r="I195" s="17" t="n"/>
       <c r="J195" s="18" t="n"/>
       <c r="K195" s="17" t="n"/>
+      <c r="L195" s="17" t="n"/>
     </row>
     <row r="196">
       <c r="A196" s="15" t="n"/>
@@ -3518,6 +3731,7 @@
       <c r="I196" s="15" t="n"/>
       <c r="J196" s="16" t="n"/>
       <c r="K196" s="15" t="n"/>
+      <c r="L196" s="15" t="n"/>
     </row>
     <row r="197">
       <c r="A197" s="17" t="n"/>
@@ -3531,6 +3745,7 @@
       <c r="I197" s="17" t="n"/>
       <c r="J197" s="18" t="n"/>
       <c r="K197" s="17" t="n"/>
+      <c r="L197" s="17" t="n"/>
     </row>
     <row r="198">
       <c r="A198" s="15" t="n"/>
@@ -3544,6 +3759,7 @@
       <c r="I198" s="15" t="n"/>
       <c r="J198" s="16" t="n"/>
       <c r="K198" s="15" t="n"/>
+      <c r="L198" s="15" t="n"/>
     </row>
     <row r="199">
       <c r="A199" s="17" t="n"/>
@@ -3557,6 +3773,7 @@
       <c r="I199" s="17" t="n"/>
       <c r="J199" s="18" t="n"/>
       <c r="K199" s="17" t="n"/>
+      <c r="L199" s="17" t="n"/>
     </row>
     <row r="200">
       <c r="A200" s="15" t="n"/>
@@ -3570,6 +3787,7 @@
       <c r="I200" s="15" t="n"/>
       <c r="J200" s="16" t="n"/>
       <c r="K200" s="15" t="n"/>
+      <c r="L200" s="15" t="n"/>
     </row>
     <row r="201">
       <c r="A201" s="17" t="n"/>
@@ -3583,6 +3801,7 @@
       <c r="I201" s="17" t="n"/>
       <c r="J201" s="18" t="n"/>
       <c r="K201" s="17" t="n"/>
+      <c r="L201" s="17" t="n"/>
     </row>
     <row r="202">
       <c r="A202" s="15" t="n"/>
@@ -3596,6 +3815,7 @@
       <c r="I202" s="15" t="n"/>
       <c r="J202" s="16" t="n"/>
       <c r="K202" s="15" t="n"/>
+      <c r="L202" s="15" t="n"/>
     </row>
     <row r="203">
       <c r="A203" s="17" t="n"/>
@@ -3609,6 +3829,7 @@
       <c r="I203" s="17" t="n"/>
       <c r="J203" s="18" t="n"/>
       <c r="K203" s="17" t="n"/>
+      <c r="L203" s="17" t="n"/>
     </row>
     <row r="204">
       <c r="A204" s="15" t="n"/>
@@ -3622,6 +3843,7 @@
       <c r="I204" s="15" t="n"/>
       <c r="J204" s="16" t="n"/>
       <c r="K204" s="15" t="n"/>
+      <c r="L204" s="15" t="n"/>
     </row>
     <row r="205">
       <c r="A205" s="17" t="n"/>
@@ -3635,6 +3857,7 @@
       <c r="I205" s="17" t="n"/>
       <c r="J205" s="18" t="n"/>
       <c r="K205" s="17" t="n"/>
+      <c r="L205" s="17" t="n"/>
     </row>
     <row r="206">
       <c r="A206" s="15" t="n"/>
@@ -3648,6 +3871,7 @@
       <c r="I206" s="15" t="n"/>
       <c r="J206" s="16" t="n"/>
       <c r="K206" s="15" t="n"/>
+      <c r="L206" s="15" t="n"/>
     </row>
     <row r="207">
       <c r="A207" s="17" t="n"/>
@@ -3661,6 +3885,7 @@
       <c r="I207" s="17" t="n"/>
       <c r="J207" s="18" t="n"/>
       <c r="K207" s="17" t="n"/>
+      <c r="L207" s="17" t="n"/>
     </row>
     <row r="208">
       <c r="A208" s="15" t="n"/>
@@ -3674,6 +3899,7 @@
       <c r="I208" s="15" t="n"/>
       <c r="J208" s="16" t="n"/>
       <c r="K208" s="15" t="n"/>
+      <c r="L208" s="15" t="n"/>
     </row>
     <row r="209">
       <c r="A209" s="17" t="n"/>
@@ -3687,6 +3913,7 @@
       <c r="I209" s="17" t="n"/>
       <c r="J209" s="18" t="n"/>
       <c r="K209" s="17" t="n"/>
+      <c r="L209" s="17" t="n"/>
     </row>
     <row r="210">
       <c r="A210" s="15" t="n"/>
@@ -3700,6 +3927,7 @@
       <c r="I210" s="15" t="n"/>
       <c r="J210" s="16" t="n"/>
       <c r="K210" s="15" t="n"/>
+      <c r="L210" s="15" t="n"/>
     </row>
     <row r="211">
       <c r="A211" s="17" t="n"/>
@@ -3713,6 +3941,7 @@
       <c r="I211" s="17" t="n"/>
       <c r="J211" s="18" t="n"/>
       <c r="K211" s="17" t="n"/>
+      <c r="L211" s="17" t="n"/>
     </row>
     <row r="212">
       <c r="A212" s="15" t="n"/>
@@ -3726,6 +3955,7 @@
       <c r="I212" s="15" t="n"/>
       <c r="J212" s="16" t="n"/>
       <c r="K212" s="15" t="n"/>
+      <c r="L212" s="15" t="n"/>
     </row>
     <row r="213">
       <c r="A213" s="17" t="n"/>
@@ -3739,6 +3969,7 @@
       <c r="I213" s="17" t="n"/>
       <c r="J213" s="18" t="n"/>
       <c r="K213" s="17" t="n"/>
+      <c r="L213" s="17" t="n"/>
     </row>
     <row r="214">
       <c r="A214" s="15" t="n"/>
@@ -3752,6 +3983,7 @@
       <c r="I214" s="15" t="n"/>
       <c r="J214" s="16" t="n"/>
       <c r="K214" s="15" t="n"/>
+      <c r="L214" s="15" t="n"/>
     </row>
     <row r="215">
       <c r="A215" s="17" t="n"/>
@@ -3765,6 +3997,7 @@
       <c r="I215" s="17" t="n"/>
       <c r="J215" s="18" t="n"/>
       <c r="K215" s="17" t="n"/>
+      <c r="L215" s="17" t="n"/>
     </row>
     <row r="216">
       <c r="A216" s="15" t="n"/>
@@ -3778,6 +4011,7 @@
       <c r="I216" s="15" t="n"/>
       <c r="J216" s="16" t="n"/>
       <c r="K216" s="15" t="n"/>
+      <c r="L216" s="15" t="n"/>
     </row>
     <row r="217">
       <c r="A217" s="17" t="n"/>
@@ -3791,6 +4025,7 @@
       <c r="I217" s="17" t="n"/>
       <c r="J217" s="18" t="n"/>
       <c r="K217" s="17" t="n"/>
+      <c r="L217" s="17" t="n"/>
     </row>
     <row r="218">
       <c r="A218" s="15" t="n"/>
@@ -3804,6 +4039,7 @@
       <c r="I218" s="15" t="n"/>
       <c r="J218" s="16" t="n"/>
       <c r="K218" s="15" t="n"/>
+      <c r="L218" s="15" t="n"/>
     </row>
     <row r="219">
       <c r="A219" s="17" t="n"/>
@@ -3817,6 +4053,7 @@
       <c r="I219" s="17" t="n"/>
       <c r="J219" s="18" t="n"/>
       <c r="K219" s="17" t="n"/>
+      <c r="L219" s="17" t="n"/>
     </row>
     <row r="220">
       <c r="A220" s="15" t="n"/>
@@ -3830,6 +4067,7 @@
       <c r="I220" s="15" t="n"/>
       <c r="J220" s="16" t="n"/>
       <c r="K220" s="15" t="n"/>
+      <c r="L220" s="15" t="n"/>
     </row>
     <row r="221">
       <c r="A221" s="17" t="n"/>
@@ -3843,6 +4081,7 @@
       <c r="I221" s="17" t="n"/>
       <c r="J221" s="18" t="n"/>
       <c r="K221" s="17" t="n"/>
+      <c r="L221" s="17" t="n"/>
     </row>
     <row r="222">
       <c r="A222" s="15" t="n"/>
@@ -3856,6 +4095,7 @@
       <c r="I222" s="15" t="n"/>
       <c r="J222" s="16" t="n"/>
       <c r="K222" s="15" t="n"/>
+      <c r="L222" s="15" t="n"/>
     </row>
     <row r="223">
       <c r="A223" s="17" t="n"/>
@@ -3869,6 +4109,7 @@
       <c r="I223" s="17" t="n"/>
       <c r="J223" s="18" t="n"/>
       <c r="K223" s="17" t="n"/>
+      <c r="L223" s="17" t="n"/>
     </row>
     <row r="224">
       <c r="A224" s="15" t="n"/>
@@ -3882,6 +4123,7 @@
       <c r="I224" s="15" t="n"/>
       <c r="J224" s="16" t="n"/>
       <c r="K224" s="15" t="n"/>
+      <c r="L224" s="15" t="n"/>
     </row>
     <row r="225">
       <c r="A225" s="17" t="n"/>
@@ -3895,6 +4137,7 @@
       <c r="I225" s="17" t="n"/>
       <c r="J225" s="18" t="n"/>
       <c r="K225" s="17" t="n"/>
+      <c r="L225" s="17" t="n"/>
     </row>
     <row r="226">
       <c r="A226" s="15" t="n"/>
@@ -3908,6 +4151,7 @@
       <c r="I226" s="15" t="n"/>
       <c r="J226" s="16" t="n"/>
       <c r="K226" s="15" t="n"/>
+      <c r="L226" s="15" t="n"/>
     </row>
     <row r="227">
       <c r="A227" s="17" t="n"/>
@@ -3921,6 +4165,7 @@
       <c r="I227" s="17" t="n"/>
       <c r="J227" s="18" t="n"/>
       <c r="K227" s="17" t="n"/>
+      <c r="L227" s="17" t="n"/>
     </row>
     <row r="228">
       <c r="A228" s="15" t="n"/>
@@ -3934,6 +4179,7 @@
       <c r="I228" s="15" t="n"/>
       <c r="J228" s="16" t="n"/>
       <c r="K228" s="15" t="n"/>
+      <c r="L228" s="15" t="n"/>
     </row>
     <row r="229">
       <c r="A229" s="17" t="n"/>
@@ -3947,6 +4193,7 @@
       <c r="I229" s="17" t="n"/>
       <c r="J229" s="18" t="n"/>
       <c r="K229" s="17" t="n"/>
+      <c r="L229" s="17" t="n"/>
     </row>
     <row r="230">
       <c r="A230" s="15" t="n"/>
@@ -3960,6 +4207,7 @@
       <c r="I230" s="15" t="n"/>
       <c r="J230" s="16" t="n"/>
       <c r="K230" s="15" t="n"/>
+      <c r="L230" s="15" t="n"/>
     </row>
     <row r="231">
       <c r="A231" s="17" t="n"/>
@@ -3973,6 +4221,7 @@
       <c r="I231" s="17" t="n"/>
       <c r="J231" s="18" t="n"/>
       <c r="K231" s="17" t="n"/>
+      <c r="L231" s="17" t="n"/>
     </row>
     <row r="232">
       <c r="A232" s="15" t="n"/>
@@ -3986,6 +4235,7 @@
       <c r="I232" s="15" t="n"/>
       <c r="J232" s="16" t="n"/>
       <c r="K232" s="15" t="n"/>
+      <c r="L232" s="15" t="n"/>
     </row>
     <row r="233">
       <c r="A233" s="17" t="n"/>
@@ -3999,6 +4249,7 @@
       <c r="I233" s="17" t="n"/>
       <c r="J233" s="18" t="n"/>
       <c r="K233" s="17" t="n"/>
+      <c r="L233" s="17" t="n"/>
     </row>
     <row r="234">
       <c r="A234" s="15" t="n"/>
@@ -4012,6 +4263,7 @@
       <c r="I234" s="15" t="n"/>
       <c r="J234" s="16" t="n"/>
       <c r="K234" s="15" t="n"/>
+      <c r="L234" s="15" t="n"/>
     </row>
     <row r="235">
       <c r="A235" s="17" t="n"/>
@@ -4025,6 +4277,7 @@
       <c r="I235" s="17" t="n"/>
       <c r="J235" s="18" t="n"/>
       <c r="K235" s="17" t="n"/>
+      <c r="L235" s="17" t="n"/>
     </row>
     <row r="236">
       <c r="A236" s="15" t="n"/>
@@ -4038,6 +4291,7 @@
       <c r="I236" s="15" t="n"/>
       <c r="J236" s="16" t="n"/>
       <c r="K236" s="15" t="n"/>
+      <c r="L236" s="15" t="n"/>
     </row>
     <row r="237">
       <c r="A237" s="17" t="n"/>
@@ -4051,6 +4305,7 @@
       <c r="I237" s="17" t="n"/>
       <c r="J237" s="18" t="n"/>
       <c r="K237" s="17" t="n"/>
+      <c r="L237" s="17" t="n"/>
     </row>
     <row r="238">
       <c r="A238" s="15" t="n"/>
@@ -4064,6 +4319,7 @@
       <c r="I238" s="15" t="n"/>
       <c r="J238" s="16" t="n"/>
       <c r="K238" s="15" t="n"/>
+      <c r="L238" s="15" t="n"/>
     </row>
     <row r="239">
       <c r="A239" s="17" t="n"/>
@@ -4077,6 +4333,7 @@
       <c r="I239" s="17" t="n"/>
       <c r="J239" s="18" t="n"/>
       <c r="K239" s="17" t="n"/>
+      <c r="L239" s="17" t="n"/>
     </row>
     <row r="240">
       <c r="A240" s="15" t="n"/>
@@ -4090,6 +4347,7 @@
       <c r="I240" s="15" t="n"/>
       <c r="J240" s="16" t="n"/>
       <c r="K240" s="15" t="n"/>
+      <c r="L240" s="15" t="n"/>
     </row>
     <row r="241">
       <c r="A241" s="17" t="n"/>
@@ -4103,6 +4361,7 @@
       <c r="I241" s="17" t="n"/>
       <c r="J241" s="18" t="n"/>
       <c r="K241" s="17" t="n"/>
+      <c r="L241" s="17" t="n"/>
     </row>
     <row r="242">
       <c r="A242" s="15" t="n"/>
@@ -4116,6 +4375,7 @@
       <c r="I242" s="15" t="n"/>
       <c r="J242" s="16" t="n"/>
       <c r="K242" s="15" t="n"/>
+      <c r="L242" s="15" t="n"/>
     </row>
     <row r="243">
       <c r="A243" s="17" t="n"/>
@@ -4129,6 +4389,7 @@
       <c r="I243" s="17" t="n"/>
       <c r="J243" s="18" t="n"/>
       <c r="K243" s="17" t="n"/>
+      <c r="L243" s="17" t="n"/>
     </row>
     <row r="244">
       <c r="A244" s="15" t="n"/>
@@ -4142,6 +4403,7 @@
       <c r="I244" s="15" t="n"/>
       <c r="J244" s="16" t="n"/>
       <c r="K244" s="15" t="n"/>
+      <c r="L244" s="15" t="n"/>
     </row>
     <row r="245">
       <c r="A245" s="17" t="n"/>
@@ -4155,6 +4417,7 @@
       <c r="I245" s="17" t="n"/>
       <c r="J245" s="18" t="n"/>
       <c r="K245" s="17" t="n"/>
+      <c r="L245" s="17" t="n"/>
     </row>
     <row r="246">
       <c r="A246" s="15" t="n"/>
@@ -4168,6 +4431,7 @@
       <c r="I246" s="15" t="n"/>
       <c r="J246" s="16" t="n"/>
       <c r="K246" s="15" t="n"/>
+      <c r="L246" s="15" t="n"/>
     </row>
     <row r="247">
       <c r="A247" s="17" t="n"/>
@@ -4181,6 +4445,7 @@
       <c r="I247" s="17" t="n"/>
       <c r="J247" s="18" t="n"/>
       <c r="K247" s="17" t="n"/>
+      <c r="L247" s="17" t="n"/>
     </row>
     <row r="248">
       <c r="A248" s="15" t="n"/>
@@ -4194,6 +4459,7 @@
       <c r="I248" s="15" t="n"/>
       <c r="J248" s="16" t="n"/>
       <c r="K248" s="15" t="n"/>
+      <c r="L248" s="15" t="n"/>
     </row>
     <row r="249">
       <c r="A249" s="17" t="n"/>
@@ -4207,6 +4473,7 @@
       <c r="I249" s="17" t="n"/>
       <c r="J249" s="18" t="n"/>
       <c r="K249" s="17" t="n"/>
+      <c r="L249" s="17" t="n"/>
     </row>
     <row r="250">
       <c r="A250" s="15" t="n"/>
@@ -4220,6 +4487,7 @@
       <c r="I250" s="15" t="n"/>
       <c r="J250" s="16" t="n"/>
       <c r="K250" s="15" t="n"/>
+      <c r="L250" s="15" t="n"/>
     </row>
     <row r="251">
       <c r="A251" s="17" t="n"/>
@@ -4233,6 +4501,7 @@
       <c r="I251" s="17" t="n"/>
       <c r="J251" s="18" t="n"/>
       <c r="K251" s="17" t="n"/>
+      <c r="L251" s="17" t="n"/>
     </row>
     <row r="252">
       <c r="A252" s="15" t="n"/>
@@ -4246,6 +4515,7 @@
       <c r="I252" s="15" t="n"/>
       <c r="J252" s="16" t="n"/>
       <c r="K252" s="15" t="n"/>
+      <c r="L252" s="15" t="n"/>
     </row>
     <row r="253">
       <c r="A253" s="17" t="n"/>
@@ -4259,6 +4529,7 @@
       <c r="I253" s="17" t="n"/>
       <c r="J253" s="18" t="n"/>
       <c r="K253" s="17" t="n"/>
+      <c r="L253" s="17" t="n"/>
     </row>
     <row r="254">
       <c r="A254" s="15" t="n"/>
@@ -4272,6 +4543,7 @@
       <c r="I254" s="15" t="n"/>
       <c r="J254" s="16" t="n"/>
       <c r="K254" s="15" t="n"/>
+      <c r="L254" s="15" t="n"/>
     </row>
     <row r="255">
       <c r="A255" s="17" t="n"/>
@@ -4285,6 +4557,7 @@
       <c r="I255" s="17" t="n"/>
       <c r="J255" s="18" t="n"/>
       <c r="K255" s="17" t="n"/>
+      <c r="L255" s="17" t="n"/>
     </row>
     <row r="256">
       <c r="A256" s="15" t="n"/>
@@ -4298,6 +4571,7 @@
       <c r="I256" s="15" t="n"/>
       <c r="J256" s="16" t="n"/>
       <c r="K256" s="15" t="n"/>
+      <c r="L256" s="15" t="n"/>
     </row>
     <row r="257">
       <c r="A257" s="17" t="n"/>
@@ -4311,6 +4585,7 @@
       <c r="I257" s="17" t="n"/>
       <c r="J257" s="18" t="n"/>
       <c r="K257" s="17" t="n"/>
+      <c r="L257" s="17" t="n"/>
     </row>
     <row r="258">
       <c r="A258" s="15" t="n"/>
@@ -4324,6 +4599,7 @@
       <c r="I258" s="15" t="n"/>
       <c r="J258" s="16" t="n"/>
       <c r="K258" s="15" t="n"/>
+      <c r="L258" s="15" t="n"/>
     </row>
     <row r="259">
       <c r="A259" s="17" t="n"/>
@@ -4337,6 +4613,7 @@
       <c r="I259" s="17" t="n"/>
       <c r="J259" s="18" t="n"/>
       <c r="K259" s="17" t="n"/>
+      <c r="L259" s="17" t="n"/>
     </row>
     <row r="260">
       <c r="A260" s="15" t="n"/>
@@ -4350,6 +4627,7 @@
       <c r="I260" s="15" t="n"/>
       <c r="J260" s="16" t="n"/>
       <c r="K260" s="15" t="n"/>
+      <c r="L260" s="15" t="n"/>
     </row>
     <row r="261">
       <c r="A261" s="17" t="n"/>
@@ -4363,6 +4641,7 @@
       <c r="I261" s="17" t="n"/>
       <c r="J261" s="18" t="n"/>
       <c r="K261" s="17" t="n"/>
+      <c r="L261" s="17" t="n"/>
     </row>
     <row r="262">
       <c r="A262" s="15" t="n"/>
@@ -4376,6 +4655,7 @@
       <c r="I262" s="15" t="n"/>
       <c r="J262" s="16" t="n"/>
       <c r="K262" s="15" t="n"/>
+      <c r="L262" s="15" t="n"/>
     </row>
     <row r="263">
       <c r="A263" s="17" t="n"/>
@@ -4389,6 +4669,7 @@
       <c r="I263" s="17" t="n"/>
       <c r="J263" s="18" t="n"/>
       <c r="K263" s="17" t="n"/>
+      <c r="L263" s="17" t="n"/>
     </row>
     <row r="264">
       <c r="A264" s="15" t="n"/>
@@ -4402,6 +4683,7 @@
       <c r="I264" s="15" t="n"/>
       <c r="J264" s="16" t="n"/>
       <c r="K264" s="15" t="n"/>
+      <c r="L264" s="15" t="n"/>
     </row>
     <row r="265">
       <c r="A265" s="17" t="n"/>
@@ -4415,6 +4697,7 @@
       <c r="I265" s="17" t="n"/>
       <c r="J265" s="18" t="n"/>
       <c r="K265" s="17" t="n"/>
+      <c r="L265" s="17" t="n"/>
     </row>
     <row r="266">
       <c r="A266" s="15" t="n"/>
@@ -4428,6 +4711,7 @@
       <c r="I266" s="15" t="n"/>
       <c r="J266" s="16" t="n"/>
       <c r="K266" s="15" t="n"/>
+      <c r="L266" s="15" t="n"/>
     </row>
     <row r="267">
       <c r="A267" s="17" t="n"/>
@@ -4441,6 +4725,7 @@
       <c r="I267" s="17" t="n"/>
       <c r="J267" s="18" t="n"/>
       <c r="K267" s="17" t="n"/>
+      <c r="L267" s="17" t="n"/>
     </row>
     <row r="268">
       <c r="A268" s="15" t="n"/>
@@ -4454,6 +4739,7 @@
       <c r="I268" s="15" t="n"/>
       <c r="J268" s="16" t="n"/>
       <c r="K268" s="15" t="n"/>
+      <c r="L268" s="15" t="n"/>
     </row>
     <row r="269">
       <c r="A269" s="17" t="n"/>
@@ -4467,6 +4753,7 @@
       <c r="I269" s="17" t="n"/>
       <c r="J269" s="18" t="n"/>
       <c r="K269" s="17" t="n"/>
+      <c r="L269" s="17" t="n"/>
     </row>
     <row r="270">
       <c r="A270" s="15" t="n"/>
@@ -4480,6 +4767,7 @@
       <c r="I270" s="15" t="n"/>
       <c r="J270" s="16" t="n"/>
       <c r="K270" s="15" t="n"/>
+      <c r="L270" s="15" t="n"/>
     </row>
     <row r="271">
       <c r="A271" s="17" t="n"/>
@@ -4493,6 +4781,7 @@
       <c r="I271" s="17" t="n"/>
       <c r="J271" s="18" t="n"/>
       <c r="K271" s="17" t="n"/>
+      <c r="L271" s="17" t="n"/>
     </row>
     <row r="272">
       <c r="A272" s="15" t="n"/>
@@ -4506,6 +4795,7 @@
       <c r="I272" s="15" t="n"/>
       <c r="J272" s="16" t="n"/>
       <c r="K272" s="15" t="n"/>
+      <c r="L272" s="15" t="n"/>
     </row>
     <row r="273">
       <c r="A273" s="17" t="n"/>
@@ -4519,6 +4809,7 @@
       <c r="I273" s="17" t="n"/>
       <c r="J273" s="18" t="n"/>
       <c r="K273" s="17" t="n"/>
+      <c r="L273" s="17" t="n"/>
     </row>
     <row r="274">
       <c r="A274" s="15" t="n"/>
@@ -4532,6 +4823,7 @@
       <c r="I274" s="15" t="n"/>
       <c r="J274" s="16" t="n"/>
       <c r="K274" s="15" t="n"/>
+      <c r="L274" s="15" t="n"/>
     </row>
     <row r="275">
       <c r="A275" s="17" t="n"/>
@@ -4545,6 +4837,7 @@
       <c r="I275" s="17" t="n"/>
       <c r="J275" s="18" t="n"/>
       <c r="K275" s="17" t="n"/>
+      <c r="L275" s="17" t="n"/>
     </row>
     <row r="276">
       <c r="A276" s="15" t="n"/>
@@ -4558,6 +4851,7 @@
       <c r="I276" s="15" t="n"/>
       <c r="J276" s="16" t="n"/>
       <c r="K276" s="15" t="n"/>
+      <c r="L276" s="15" t="n"/>
     </row>
     <row r="277">
       <c r="A277" s="17" t="n"/>
@@ -4571,6 +4865,7 @@
       <c r="I277" s="17" t="n"/>
       <c r="J277" s="18" t="n"/>
       <c r="K277" s="17" t="n"/>
+      <c r="L277" s="17" t="n"/>
     </row>
     <row r="278">
       <c r="A278" s="15" t="n"/>
@@ -4584,6 +4879,7 @@
       <c r="I278" s="15" t="n"/>
       <c r="J278" s="16" t="n"/>
       <c r="K278" s="15" t="n"/>
+      <c r="L278" s="15" t="n"/>
     </row>
     <row r="279">
       <c r="A279" s="17" t="n"/>
@@ -4597,6 +4893,7 @@
       <c r="I279" s="17" t="n"/>
       <c r="J279" s="18" t="n"/>
       <c r="K279" s="17" t="n"/>
+      <c r="L279" s="17" t="n"/>
     </row>
     <row r="280">
       <c r="A280" s="15" t="n"/>
@@ -4610,6 +4907,7 @@
       <c r="I280" s="15" t="n"/>
       <c r="J280" s="16" t="n"/>
       <c r="K280" s="15" t="n"/>
+      <c r="L280" s="15" t="n"/>
     </row>
     <row r="281">
       <c r="A281" s="17" t="n"/>
@@ -4623,6 +4921,7 @@
       <c r="I281" s="17" t="n"/>
       <c r="J281" s="18" t="n"/>
       <c r="K281" s="17" t="n"/>
+      <c r="L281" s="17" t="n"/>
     </row>
     <row r="282">
       <c r="A282" s="15" t="n"/>
@@ -4636,6 +4935,7 @@
       <c r="I282" s="15" t="n"/>
       <c r="J282" s="16" t="n"/>
       <c r="K282" s="15" t="n"/>
+      <c r="L282" s="15" t="n"/>
     </row>
     <row r="283">
       <c r="A283" s="17" t="n"/>
@@ -4649,6 +4949,7 @@
       <c r="I283" s="17" t="n"/>
       <c r="J283" s="18" t="n"/>
       <c r="K283" s="17" t="n"/>
+      <c r="L283" s="17" t="n"/>
     </row>
     <row r="284">
       <c r="A284" s="15" t="n"/>
@@ -4662,6 +4963,7 @@
       <c r="I284" s="15" t="n"/>
       <c r="J284" s="16" t="n"/>
       <c r="K284" s="15" t="n"/>
+      <c r="L284" s="15" t="n"/>
     </row>
     <row r="285">
       <c r="A285" s="17" t="n"/>
@@ -4675,6 +4977,7 @@
       <c r="I285" s="17" t="n"/>
       <c r="J285" s="18" t="n"/>
       <c r="K285" s="17" t="n"/>
+      <c r="L285" s="17" t="n"/>
     </row>
     <row r="286">
       <c r="A286" s="15" t="n"/>
@@ -4688,6 +4991,7 @@
       <c r="I286" s="15" t="n"/>
       <c r="J286" s="16" t="n"/>
       <c r="K286" s="15" t="n"/>
+      <c r="L286" s="15" t="n"/>
     </row>
     <row r="287">
       <c r="A287" s="17" t="n"/>
@@ -4701,6 +5005,7 @@
       <c r="I287" s="17" t="n"/>
       <c r="J287" s="18" t="n"/>
       <c r="K287" s="17" t="n"/>
+      <c r="L287" s="17" t="n"/>
     </row>
     <row r="288">
       <c r="A288" s="15" t="n"/>
@@ -4714,6 +5019,7 @@
       <c r="I288" s="15" t="n"/>
       <c r="J288" s="16" t="n"/>
       <c r="K288" s="15" t="n"/>
+      <c r="L288" s="15" t="n"/>
     </row>
     <row r="289">
       <c r="A289" s="17" t="n"/>
@@ -4727,6 +5033,7 @@
       <c r="I289" s="17" t="n"/>
       <c r="J289" s="18" t="n"/>
       <c r="K289" s="17" t="n"/>
+      <c r="L289" s="17" t="n"/>
     </row>
     <row r="290">
       <c r="A290" s="15" t="n"/>
@@ -4740,6 +5047,7 @@
       <c r="I290" s="15" t="n"/>
       <c r="J290" s="16" t="n"/>
       <c r="K290" s="15" t="n"/>
+      <c r="L290" s="15" t="n"/>
     </row>
     <row r="291">
       <c r="A291" s="17" t="n"/>
@@ -4753,6 +5061,7 @@
       <c r="I291" s="17" t="n"/>
       <c r="J291" s="18" t="n"/>
       <c r="K291" s="17" t="n"/>
+      <c r="L291" s="17" t="n"/>
     </row>
     <row r="292">
       <c r="A292" s="15" t="n"/>
@@ -4766,6 +5075,7 @@
       <c r="I292" s="15" t="n"/>
       <c r="J292" s="16" t="n"/>
       <c r="K292" s="15" t="n"/>
+      <c r="L292" s="15" t="n"/>
     </row>
     <row r="293">
       <c r="A293" s="17" t="n"/>
@@ -4779,6 +5089,7 @@
       <c r="I293" s="17" t="n"/>
       <c r="J293" s="18" t="n"/>
       <c r="K293" s="17" t="n"/>
+      <c r="L293" s="17" t="n"/>
     </row>
     <row r="294">
       <c r="A294" s="15" t="n"/>
@@ -4792,6 +5103,7 @@
       <c r="I294" s="15" t="n"/>
       <c r="J294" s="16" t="n"/>
       <c r="K294" s="15" t="n"/>
+      <c r="L294" s="15" t="n"/>
     </row>
     <row r="295">
       <c r="A295" s="17" t="n"/>
@@ -4805,6 +5117,7 @@
       <c r="I295" s="17" t="n"/>
       <c r="J295" s="18" t="n"/>
       <c r="K295" s="17" t="n"/>
+      <c r="L295" s="17" t="n"/>
     </row>
     <row r="296">
       <c r="A296" s="15" t="n"/>
@@ -4818,6 +5131,7 @@
       <c r="I296" s="15" t="n"/>
       <c r="J296" s="16" t="n"/>
       <c r="K296" s="15" t="n"/>
+      <c r="L296" s="15" t="n"/>
     </row>
     <row r="297">
       <c r="A297" s="17" t="n"/>
@@ -4831,6 +5145,7 @@
       <c r="I297" s="17" t="n"/>
       <c r="J297" s="18" t="n"/>
       <c r="K297" s="17" t="n"/>
+      <c r="L297" s="17" t="n"/>
     </row>
     <row r="298">
       <c r="A298" s="15" t="n"/>
@@ -4844,6 +5159,7 @@
       <c r="I298" s="15" t="n"/>
       <c r="J298" s="16" t="n"/>
       <c r="K298" s="15" t="n"/>
+      <c r="L298" s="15" t="n"/>
     </row>
     <row r="299">
       <c r="A299" s="17" t="n"/>
@@ -4857,6 +5173,7 @@
       <c r="I299" s="17" t="n"/>
       <c r="J299" s="18" t="n"/>
       <c r="K299" s="17" t="n"/>
+      <c r="L299" s="17" t="n"/>
     </row>
     <row r="300">
       <c r="A300" s="15" t="n"/>
@@ -4870,6 +5187,7 @@
       <c r="I300" s="15" t="n"/>
       <c r="J300" s="16" t="n"/>
       <c r="K300" s="15" t="n"/>
+      <c r="L300" s="15" t="n"/>
     </row>
     <row r="301">
       <c r="A301" s="17" t="n"/>
@@ -4883,9 +5201,10 @@
       <c r="I301" s="17" t="n"/>
       <c r="J301" s="18" t="n"/>
       <c r="K301" s="17" t="n"/>
+      <c r="L301" s="17" t="n"/>
     </row>
   </sheetData>
-  <dataValidations count="8">
+  <dataValidations count="9">
     <dataValidation sqref="B2:B301" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Check this value" error="Pick a member from the Members sheet, or type a new name to add them automatically." promptTitle="Member" prompt="Pick a member from the Members sheet, or type a new name to add them automatically." type="list" errorStyle="warning">
       <formula1>=Members!$A$2:$A$41</formula1>
     </dataValidation>
@@ -4911,6 +5230,9 @@
     <dataValidation sqref="K2:K301" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Check this value" error="Estimated hours, e.g. 2 or 1.5." promptTitle="Est Hours" prompt="Estimated hours, e.g. 2 or 1.5." type="decimal" operator="greaterThanOrEqual">
       <formula1>0</formula1>
     </dataValidation>
+    <dataValidation sqref="L2:L301" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Module" prompt="Which module is this task against? Pick from the list or type your own." type="list">
+      <formula1>=Modules!$A$2:$A$41</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5352,4 +5674,196 @@
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="14" t="inlineStr">
+        <is>
+          <t>Module</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="15" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="17" t="inlineStr">
+        <is>
+          <t>Purchase</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="15" t="inlineStr">
+        <is>
+          <t>Inventory</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="17" t="inlineStr">
+        <is>
+          <t>Accounting</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="15" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="17" t="inlineStr">
+        <is>
+          <t>HR / Payroll</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="15" t="inlineStr">
+        <is>
+          <t>Manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="17" t="inlineStr">
+        <is>
+          <t>Projects</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="15" t="inlineStr">
+        <is>
+          <t>Website / eCommerce</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="17" t="inlineStr">
+        <is>
+          <t>Reporting / BI</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t>IT Infrastructure</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="17" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="15" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="17" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="15" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="17" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="15" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="17" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="15" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="17" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="15" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="17" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="15" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="17" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="15" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="17" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="15" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="17" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="15" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="17" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="15" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="17" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="15" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="17" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="15" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="17" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="15" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="17" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="15" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="17" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>